--- a/downloads/Trainory_Quarterly_Access_Review_and_Audit_Evidence.xlsx
+++ b/downloads/Trainory_Quarterly_Access_Review_and_Audit_Evidence.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R4870bb895ef54a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access Review" sheetId="2" r:id="Re9a31437de4d4dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="R19df401dd7694cfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Log" sheetId="4" r:id="R7678960ab46c4904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviewer Guide" sheetId="5" r:id="R95b3567733204bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="Rad85572668d54111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access Review" sheetId="2" r:id="Recc2adbba1504bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="Ra16840aeee6740f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Log" sheetId="4" r:id="R2479b878d5504794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviewer Guide" sheetId="5" r:id="R2c86531e68d64c1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -132,8 +132,20 @@
       <x:color rgb="FF0B2545"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -163,6 +175,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF8FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -268,7 +340,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="154">
+  <x:cellXfs count="168">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -641,6 +713,48 @@
     <x:xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -652,7 +766,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -663,7 +777,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -674,7 +788,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -685,7 +799,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -696,7 +810,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -707,7 +821,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -718,7 +832,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -729,7 +843,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -740,7 +854,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -751,7 +865,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -762,7 +876,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -773,7 +887,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -784,7 +898,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -794,7 +908,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -805,7 +919,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -960,7 +1074,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R90639d5c4aa34c88"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R42e61c860c6d46a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1263,17 +1377,35 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="61" t="str">
-        <x:v>Step 8 | User access certification and audit-evidence package | Q4 2026</x:v>
-      </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
-      <x:c r="D2" s="61"/>
-      <x:c r="E2" s="61"/>
-      <x:c r="F2" s="61"/>
-      <x:c r="G2" s="61"/>
-      <x:c r="H2" s="61"/>
-      <x:c r="I2" s="61"/>
-      <x:c r="J2" s="61"/>
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="B2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="C2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="D2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="E2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="F2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="G2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="H2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="I2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
+      <x:c r="J2" s="61" t="str">
+        <x:v>User access certification and audit-evidence package | Q4 2026</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62"/>
@@ -1737,10 +1869,14 @@
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="81" t="str">
-        <x:v>Portfolio disclaimer: All people, access records, systems, evidence, findings, and approvals in this workbook are fictional and created for an educational GRC portfolio.</x:v>
-      </x:c>
-      <x:c r="B31" s="81"/>
-      <x:c r="C31" s="81"/>
+        <x:v>Case study note: All people, access records, systems, evidence, findings, and approvals are fictional.</x:v>
+      </x:c>
+      <x:c r="B31" s="81" t="str">
+        <x:v>Case study note: All people, access records, systems, evidence, findings, and approvals are fictional.</x:v>
+      </x:c>
+      <x:c r="C31" s="81" t="str">
+        <x:v>Case study note: All people, access records, systems, evidence, findings, and approvals are fictional.</x:v>
+      </x:c>
       <x:c r="D31" s="81"/>
       <x:c r="E31" s="81"/>
       <x:c r="F31" s="81"/>
@@ -1758,7 +1894,7 @@
     <x:mergeCell ref="A31:J31"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2d94f6473040a3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38332fc19b634a0d"/>
 </x:worksheet>
 </file>
 
@@ -4239,7 +4375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9147fe6af21f4a31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3654a28f2094f77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5067,7 +5203,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ac09f07065945d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e018e3cc594ba4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5667,7 +5803,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c610b2d5b54847"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13bb6d1ac1414074"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5681,24 +5817,32 @@
     <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="60" t="str">
-        <x:v>Reviewer Guide</x:v>
-      </x:c>
-      <x:c r="B1" s="60"/>
-      <x:c r="C1" s="60"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="166" t="str">
+        <x:v>Access Review Methodology</x:v>
+      </x:c>
+      <x:c r="B1" s="166" t="str">
+        <x:v>Access Review Methodology</x:v>
+      </x:c>
+      <x:c r="C1" s="166" t="str">
+        <x:v>Access Review Methodology</x:v>
+      </x:c>
       <x:c r="D1" s="60"/>
       <x:c r="E1" s="60"/>
       <x:c r="F1" s="60"/>
       <x:c r="G1" s="60"/>
       <x:c r="H1" s="60"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="61" t="str">
-        <x:v>How to review and explain the Trainory access-certification package</x:v>
-      </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="167" t="str">
+        <x:v>Review steps, evidence requirements, and key terms</x:v>
+      </x:c>
+      <x:c r="B2" s="167" t="str">
+        <x:v>Review steps, evidence requirements, and key terms</x:v>
+      </x:c>
+      <x:c r="C2" s="167" t="str">
+        <x:v>Review steps, evidence requirements, and key terms</x:v>
+      </x:c>
       <x:c r="D2" s="61"/>
       <x:c r="E2" s="61"/>
       <x:c r="F2" s="61"/>
@@ -5914,9 +6058,7 @@
       <x:c r="H18" s="62"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="63" t="str">
-        <x:v>Interview-ready explanation</x:v>
-      </x:c>
+      <x:c r="A19" s="63"/>
       <x:c r="B19" s="64"/>
       <x:c r="C19" s="64"/>
       <x:c r="D19" s="64"/>
@@ -5926,9 +6068,7 @@
       <x:c r="H19" s="65"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="145" t="str">
-        <x:v>I performed a fictional quarterly access review for Trainory across cloud, source-code, customer-data, support, analytics, payment, and collaboration systems. I reconciled the account population, reviewed employment status and business need, checked MFA and privilege levels, and documented management decisions. The review identified a terminated contractor account, excessive production and database permissions, a vendor account without an expiration date, and a privileged service account without an owner. I converted those exceptions into tracked findings with owners, deadlines, residual-risk estimates, and specific closure evidence.</x:v>
-      </x:c>
+      <x:c r="A20" s="145"/>
       <x:c r="B20" s="146"/>
       <x:c r="C20" s="146"/>
       <x:c r="D20" s="146"/>
@@ -6119,7 +6259,7 @@
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="81" t="str">
-        <x:v>Portfolio disclaimer: This workbook uses fictional identities, systems, evidence, and approvals. It is an educational artifact, not an actual audit or certification.</x:v>
+        <x:v>Case study note: Trainory and all review data are fictional.</x:v>
       </x:c>
       <x:c r="B36" s="81"/>
       <x:c r="C36" s="81"/>
@@ -6131,8 +6271,6 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="A5:H8"/>
     <x:mergeCell ref="A10:H10"/>
@@ -6140,6 +6278,8 @@
     <x:mergeCell ref="A20:H25"/>
     <x:mergeCell ref="A27:H27"/>
     <x:mergeCell ref="A36:H36"/>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
